--- a/June/29.06.2026/northwind.xlsx
+++ b/June/29.06.2026/northwind.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19160" windowHeight="16500" firstSheet="10" activeTab="14"/>
+    <workbookView windowWidth="28000" windowHeight="12360" firstSheet="10" activeTab="14"/>
   </bookViews>
   <sheets>
     <sheet name="categories" sheetId="1" r:id="rId1"/>
@@ -8606,7 +8606,7 @@
     <row r="1" spans="1:2">
       <c r="A1" s="1">
         <f ca="1">TODAY()</f>
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="B1" t="s">
         <v>1500</v>
